--- a/artfynd/A 24767-2024 artfynd.xlsx
+++ b/artfynd/A 24767-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>59756887</v>
+        <v>59756801</v>
       </c>
       <c r="B3" t="n">
-        <v>95511</v>
+        <v>96251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,43 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grytsjöskogen, S om Norrlången, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594747.7716330388</v>
+        <v>594698.513175918</v>
       </c>
       <c r="R3" t="n">
-        <v>6567361.065568615</v>
+        <v>6567300.458009335</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +891,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Berg, lav- och mossbevuxet, i barrskog</t>
+          <t>Barrskog, vid stig</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,123 +906,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>59756801</v>
-      </c>
-      <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Grytsjöskogen, S om Norrlången, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>594698.513175918</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6567300.458009335</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2016-05-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2016-05-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog, vid stig</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
